--- a/LISTAS_ORDENADAS/MI/Soportes y escuadras/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Soportes y escuadras/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="15" min="1" max="1"/>
@@ -799,14 +799,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45154.58664776727</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -848,16 +844,6 @@
       <c r="A11" s="23" t="n"/>
       <c r="E11" s="6" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="18" customHeight="1" s="15">
       <c r="A22" s="8" t="inlineStr">
         <is>
@@ -1075,23 +1061,22 @@
       </c>
       <c r="F44" s="11" t="n"/>
     </row>
-    <row r="45"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
